--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-02.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-02.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,37 +1175,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOSNIA 1</t>
+          <t>ENGLAND 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Borac Banja Luka x Zeljeznicar</t>
+          <t>Millwall x Wrexham</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zeljeznicar</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1214,20 +1214,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>18.52</v>
+        <v>6.25</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1259,32 +1259,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ENGLAND 2</t>
+          <t>SCOTLAND 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Millwall x Wrexham</t>
+          <t>Celtic x Aberdeen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,20 +1293,20 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="L11" t="n">
-        <v>6.25</v>
+        <v>16.13</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1333,27 +1333,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SCOTLAND 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Celtic x Aberdeen</t>
+          <t>Flamengo x Mirassol</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1372,20 +1372,20 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="K12" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="L12" t="n">
-        <v>16.13</v>
+        <v>15.15</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1412,37 +1412,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>BOSNIA 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Flamengo x Mirassol</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Mirassol</t>
-        </is>
-      </c>
+          <t>Borac Banja Luka x Zeljeznicar</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,13 +1443,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="L13" t="n">
-        <v>15.15</v>
+        <v>7.14</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
@@ -1469,92 +1461,21 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>BOSNIA 1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Borac Banja Luka x Zeljeznicar</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Match Odds (Away)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="M14" t="n">
-        <v>100</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2x0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-02.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-02.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4x2</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -990,12 +990,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-02.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-02.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -595,12 +595,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4x2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -753,12 +753,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -990,12 +990,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
